--- a/amostras/principal/P09/matriz_rastreabilidade_P09.xlsx
+++ b/amostras/principal/P09/matriz_rastreabilidade_P09.xlsx
@@ -514,6 +514,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -811,6 +812,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -868,6 +870,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -922,27 +925,28 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Não Aplicável</t>
-        </is>
-      </c>
+          <t>Nenhuma</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Não Aplicável</t>
+          <t>Nenhum</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Amostra Não Preenchida</t>
+          <t>Nenhuma / Sem Achados</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Não Aplicável</t>
+          <t>Nenhuma</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Aguardando geração (Passo 1 pendente)</t>
+          <t>Não se aplica (amostra limpa)</t>
         </is>
       </c>
     </row>
@@ -982,6 +986,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1039,6 +1044,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1096,6 +1102,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1153,6 +1160,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1210,6 +1218,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1267,6 +1276,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1684,6 +1694,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1741,6 +1752,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Nenhum</t>
